--- a/backend/data/excel/2bf344b1ec86_data.xlsx
+++ b/backend/data/excel/2bf344b1ec86_data.xlsx
@@ -542,7 +542,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2025-09-09 09:13:51</t>
+          <t>2025-09-10 09:32:17</t>
         </is>
       </c>
     </row>

--- a/backend/data/excel/2bf344b1ec86_data.xlsx
+++ b/backend/data/excel/2bf344b1ec86_data.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -613,201 +613,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2025-09-21 18:40:41</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>통계정보상세</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>통계정보/작성(조사)대상</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>○ 건축법 제11조의 건축허가 대상 주택 ○ 건축법 제14조의 건축신고 대상 주택 ○ 주택법 제15조의 주택건설사업 사업계획승인 대상 주택</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>통계정보상세</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>통계정보/작성(조사)근거</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>○ 승인번호 제116026호(승인일자 2002-04-03) ○ 주택건설실적(분양) 승인 통계 변경(변경승인일자 2020-12-30)
-○ 통계법 제18조 규정에 의한 승인통계지정, 통계법 제27조 규정에 의한 통계공표.
-○ 건축법 제11조 건축법 제14조 주택법 제15조</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>통계정보상세</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>통계정보/작성(조사)목적</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>주택정책 수립 관련 정책자료 활용</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>통계정보상세</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>통계정보/공표주기</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>익월말</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>통계정보상세</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>통계정보/공표방법</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>「국토교통통계연보」, 보도자료, 국토교통통계누리(http://stat.molit.go.kr)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>통계정보상세</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>통계정보/주석</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>1) 주)(-)수치는 취소 등의 사유로 정정 과정에서 발생
-자료 : 국토교통부 주택토지실 주택정책관 주택정책과
-2) 2023년(1~12월) 주택건설((인허가, 착공, 준공) 실적 수정 공표(2024.4.30.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>통계정보상세</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>메인페이지/검색분야</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>주택/주택건설실적통계(준공)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>통계정보상세</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>메인페이지/담당부서</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>주택정책과 (곽경래, ☏ 0442014148)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>용어정의</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>관련용어/주요항목</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>단독(다가구)는 동수 기준임.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>용어정의</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>관련용어/의미분석</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>관련용어
-등록된 관련 용어가 없습니다.
-승인통계는 로 표시됩니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>용어정의</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>관련용어/관련용어</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>등록된 관련 용어가 없습니다.
-승인통계는 로 표시됩니다.</t>
+          <t>2025-09-21 22:32:44</t>
         </is>
       </c>
     </row>
